--- a/servers/maze_main_server/conf.d/data/maze_item_attr_v8【迷宫-道具-道具id对应属性id】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_item_attr_v8【迷宫-道具-道具id对应属性id】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4E6D28-BBFA-4C14-827A-76F2D3288F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB44181-07DD-442B-8D69-B922DC9C4024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4BF97ACB-F0BA-43EF-B194-721BB819C92D}"/>
   </bookViews>
@@ -36,10 +36,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t>对应的属性id（走属性对应技能逻辑）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>道具id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -61,6 +57,10 @@
   </si>
   <si>
     <t>paipaiworld_config</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能属性id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -448,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14621CF8-8009-4878-BAE6-5D83C2C16AC4}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
@@ -457,31 +457,31 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -489,48 +489,23 @@
         <v>48300001</v>
       </c>
       <c r="B5">
-        <v>4590900</v>
+        <v>990001</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>48300002</v>
-      </c>
-      <c r="B6">
-        <v>3540100</v>
-      </c>
+      <c r="A6" s="1"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>48300003</v>
-      </c>
-      <c r="B7">
-        <v>3540300</v>
-      </c>
+      <c r="A7" s="1"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>48300004</v>
-      </c>
-      <c r="B8">
-        <v>3540500</v>
-      </c>
+      <c r="A8" s="1"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>48300005</v>
-      </c>
-      <c r="B9">
-        <v>3540700</v>
-      </c>
+      <c r="A9" s="1"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>48300006</v>
-      </c>
-      <c r="B10">
-        <v>3541100</v>
-      </c>
+      <c r="A10" s="1"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
@@ -540,21 +515,6 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="1"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
